--- a/PC_Cases_Cleaned.xlsx
+++ b/PC_Cases_Cleaned.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K184"/>
+  <dimension ref="A1:L184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -463,12 +463,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -514,15 +515,20 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Tags</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Sales Velocity</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -563,15 +569,20 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>black, cable-management, compact, dual-chamber, high-airflow, mid-tower, panoramic-glass</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>50+ bought in past month</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -612,15 +623,20 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
+          <t>mid-tower, white</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
           <t>100+ bought in past month</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -659,13 +675,18 @@
           <t>h5</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, compact, high-airflow, mid-tower, radiator-support, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -704,13 +725,18 @@
           <t>xt</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, quiet-design</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -749,13 +775,18 @@
           <t>216</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>black, high-airflow, mid-tower, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -794,13 +825,18 @@
           <t>y60</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>atx, dual-chamber, gaming, mid-tower, panoramic-glass, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -839,13 +875,18 @@
           <t>3000d</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>black, gpu-support, high-airflow, mid-tower, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -884,13 +925,18 @@
           <t>120a</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>atx, dust-filters, gpu-support, high-airflow, magnetic-filters, mid-tower, red, rgb-lighting, tempered-glass, usb-3.2</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -931,15 +977,20 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>mid-tower, red, rgb-lighting, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>100+ bought in past month</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -978,13 +1029,18 @@
           <t>flash</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>atx, compact, gaming, micro-atx, red, rgb-lighting, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1023,13 +1079,18 @@
           <t>design</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>black, mid-tower, quiet-design, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1068,13 +1129,18 @@
           <t>h3</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, gpu-support, high-airflow, micro-atx</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1113,13 +1179,18 @@
           <t>mcv4</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>black, dual-chamber, e-atx, frameless, gaming, modular, red, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1158,13 +1229,18 @@
           <t>112r</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>atx, dust-filters, magnetic-filters, mesh-front, micro-atx, mid-tower, mini-itx, red, rgb-lighting, tempered-glass, usb-3.2</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1203,13 +1279,18 @@
           <t>a3</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>atx, micro-atx, white</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1248,13 +1329,18 @@
           <t>c8,</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>dual-chamber, e-atx, full-tower, high-airflow, radiator-support, red, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1293,13 +1379,18 @@
           <t>o11d</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>black, dual-chamber, e-atx, mid-tower, modular, red, rgb-lighting, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1340,15 +1431,20 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
+          <t>atx, black, dual-chamber, radiator-support, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
           <t>50+ bought in past month</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1389,15 +1485,20 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>atx, black, dual-chamber, micro-atx</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>50+ bought in past month</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1436,13 +1537,18 @@
           <t>gt301</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>atx, compact, gaming, honeycomb-mesh, mid-tower, radiator-support, red, rgb-lighting, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1481,13 +1587,18 @@
           <t>zeus</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>atx, gaming, high-airflow, mid-tower, red, rgb-lighting, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1526,13 +1637,18 @@
           <t>100r</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>atx, dual-chamber, dust-filters, e-atx, gpu-anti-sag, gpu-support, usb-type-c, white</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1571,13 +1687,18 @@
           <t>h7</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>mid-tower, rgb-lighting, white</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1616,13 +1737,18 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr"/>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>black, compact, mid-tower</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1661,13 +1787,18 @@
           <t>e3</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>atx, dust-filters, gaming, magnetic-filters, mesh-front, mid-tower, red, rgb-lighting, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1706,13 +1837,18 @@
           <t>c8</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr"/>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>dual-chamber, e-atx, full-tower, high-airflow, radiator-support, red, side-panel-glass, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1753,15 +1889,20 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>atx, black, mesh-front, mid-tower, red, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>100+ bought in past month</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1800,13 +1941,18 @@
           <t>jet</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr"/>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>atx, e-atx, mid-tower</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1847,15 +1993,20 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>black, high-airflow, mid-tower, panoramic-glass, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>50+ bought in past month</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1894,13 +2045,18 @@
           <t>600</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr"/>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>black, quiet-design</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1939,13 +2095,18 @@
           <t>217</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>black, gpu-support, mid-tower, modular, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -1984,13 +2145,18 @@
           <t>5000d</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>high-airflow, mid-tower, rgb-lighting, white</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2029,13 +2195,18 @@
           <t>f600</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, e-atx, gaming, high-airflow, mid-tower, radiator-support, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2072,13 +2243,18 @@
           <t>207</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, high-airflow, micro-atx, mid-tower, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2119,15 +2295,20 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
+          <t>atx, black, full-tower, gaming, mid-tower, panoramic-glass, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>50+ bought in past month</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2168,15 +2349,20 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
+          <t>atx, black, e-atx, gaming, high-airflow, mesh-front, mid-tower, radiator-support, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
           <t>50+ bought in past month</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2217,15 +2403,20 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
+          <t>atx, black, e-atx, gaming, high-airflow, mid-tower, radiator-support, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>100+ bought in past month</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2266,15 +2457,20 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
+          <t>atx, dust-filters, gpu-support, high-airflow, magnetic-filters, mid-tower, red, rgb-lighting, tempered-glass, usb-3.2, usb-type-c</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
           <t>100+ bought in past month</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2313,13 +2509,18 @@
           <t>mc-se2,</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>atx, compact, dual-chamber, frameless, gaming, micro-atx, red, rgb-lighting, side-panel-glass, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2358,13 +2559,18 @@
           <t>kz08</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr"/>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, mid-tower, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2403,13 +2609,18 @@
           <t>2500x</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, dual-chamber, micro-atx, panoramic-glass, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2448,13 +2659,18 @@
           <t>4500x</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>black, gpu-anti-sag, gpu-support, mid-tower, panoramic-glass, radiator-support, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2493,13 +2709,18 @@
           <t>citadel</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, mesh-front, micro-atx</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2538,13 +2759,18 @@
           <t>(mg-ne620qi_dbk02)</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr"/>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, dual-chamber, mid-tower, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2583,13 +2809,18 @@
           <t>li</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, high-airflow, mesh-front, micro-atx, mid-tower, red, rgb-lighting, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2630,15 +2861,20 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
+          <t>atx, black, gaming, mid-tower, panoramic-glass, red, rgb-lighting, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
           <t>50+ bought in past month</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2677,13 +2913,18 @@
           <t>void</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>black, gaming, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="L48" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2722,13 +2963,18 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr"/>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>atx, gaming, panoramic-glass, red, rgb-lighting, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2767,13 +3013,18 @@
           <t>mid</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>atx, gaming, mid-tower, red, rgb-lighting, side-panel-glass, tempered-glass, wood</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2814,15 +3065,20 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
+          <t>atx, black, e-atx, gaming, mid-tower, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
           <t>50+ bought in past month</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2863,15 +3119,20 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
+          <t>atx, black, gaming, mid-tower, panoramic-glass, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>50+ bought in past month</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2908,13 +3169,18 @@
           <t>h2</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr"/>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>compact, high-airflow, mini-itx, white</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2953,13 +3219,18 @@
           <t>m100r</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, micro-atx, mid-tower, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -2998,13 +3269,18 @@
           <t>vsk-4000b-u3/u2</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr"/>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>atx, black</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3043,13 +3319,18 @@
           <t>2500d</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, dual-chamber, high-airflow, micro-atx, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K56" s="3" t="inlineStr">
+      <c r="L56" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3090,15 +3371,20 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
+          <t>atx, black, dual-chamber, gaming, mid-tower, radiator-support, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
           <t>50+ bought in past month</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3137,13 +3423,18 @@
           <t>100l</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>atx, dual-chamber, dust-filters, e-atx, gpu-anti-sag, gpu-support, usb-type-c, white</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3182,13 +3473,18 @@
           <t>a31</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr"/>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>atx, cable-management, e-atx, frameless, gaming, high-airflow, mid-tower, red, rgb-lighting, side-panel-glass, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3225,13 +3521,18 @@
           <t>atx</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>atx, gaming, mid-tower, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3270,13 +3571,18 @@
           <t>inspire-pk</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr"/>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>atx, gaming, high-airflow, magnetic-filters, mesh-front, metal, mid-tower, pink, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3317,15 +3623,20 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
+          <t>atx, black, e-atx, gaming, mid-tower, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>50+ bought in past month</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3364,13 +3675,18 @@
           <t>sauron</t>
         </is>
       </c>
-      <c r="I63" s="4" t="inlineStr"/>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, red, rgb-lighting, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3409,13 +3725,18 @@
           <t>m1</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, e-atx, gaming, high-airflow, mid-tower, radiator-support, rgb-lighting, wood</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3454,13 +3775,18 @@
           <t>gaming</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr"/>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>atx, gaming, mini-itx, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3499,13 +3825,18 @@
           <t>y70</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>atx, dual-chamber, mid-tower</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K66" s="3" t="inlineStr">
+      <c r="L66" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3544,13 +3875,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr"/>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>atx, dual-chamber, mid-tower, red, rgb-lighting, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr"/>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3589,13 +3925,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>atx, compact, gaming, high-airflow, mesh-front, micro-atx, red, rgb-lighting, side-panel-glass, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3634,13 +3975,18 @@
           <t>atx</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr"/>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K69" s="5" t="inlineStr">
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, cable-management, e-atx, gaming, high-airflow, mid-tower, radiator-support, red, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr"/>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3679,13 +4025,18 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, e-atx, gaming, mid-tower, radiator-support, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3724,13 +4075,18 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>black, mid-tower, panoramic-glass, radiator-support, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3769,13 +4125,18 @@
           <t>mi2-a</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, high-airflow, mesh-front, micro-atx, panoramic-glass, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3814,13 +4175,18 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr"/>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K73" s="5" t="inlineStr">
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, micro-atx</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3859,13 +4225,18 @@
           <t>hyxn</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K74" s="3" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, compact, gaming, mid-tower, radiator-support, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3904,13 +4275,18 @@
           <t>xtender</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr"/>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K75" s="5" t="inlineStr">
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>black, e-atx, full-tower, panoramic-glass, radiator-support, red, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr"/>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3949,13 +4325,18 @@
           <t>y40</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>atx, mid-tower, red</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K76" s="3" t="inlineStr">
+      <c r="L76" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -3994,13 +4375,18 @@
           <t>mentor</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr"/>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K77" s="5" t="inlineStr">
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, compact, micro-atx</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr"/>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4039,13 +4425,18 @@
           <t>case</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, dual-chamber, gaming, mid-tower, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4084,13 +4475,18 @@
           <t>apex</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr"/>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K79" s="5" t="inlineStr">
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>atx, dual-chamber, gaming, mid-tower, red, rgb-lighting, tempered-glass, wood</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr"/>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4129,13 +4525,18 @@
           <t>x50</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>atx, mid-tower, white</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K80" s="3" t="inlineStr">
+      <c r="L80" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4172,13 +4573,18 @@
           <t>flux</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr"/>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K81" s="5" t="inlineStr">
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>atx, e-atx, quiet-design</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr"/>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4217,13 +4623,18 @@
           <t>atx</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K82" s="3" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, mid-tower, red, rgb-lighting, tempered-glass, wood</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4262,13 +4673,18 @@
           <t>v3</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K83" s="5" t="inlineStr">
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, gpu-support, high-airflow, micro-atx, radiator-support, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4307,13 +4723,18 @@
           <t>kz-z</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K84" s="3" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>atx, dual-chamber, gaming, mid-tower, red, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4352,13 +4773,18 @@
           <t>c7</t>
         </is>
       </c>
-      <c r="I85" s="4" t="inlineStr"/>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K85" s="5" t="inlineStr">
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>gaming, mid-tower, red, rgb-lighting, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr"/>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4395,13 +4821,18 @@
           <t>tg3</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, gpu-support, high-airflow, mid-tower, radiator-support</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4440,13 +4871,18 @@
           <t>pc</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr"/>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K87" s="5" t="inlineStr">
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, dual-chamber, mid-tower, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr"/>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4485,13 +4921,18 @@
           <t>(2026)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, dual-chamber, e-atx, gaming, high-airflow, mid-tower</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4530,13 +4971,18 @@
           <t>p1</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr"/>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K89" s="5" t="inlineStr">
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>atx, cable-management, dual-chamber, e-atx, full-tower, gaming, high-airflow, modular, panoramic-glass, red, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr"/>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4575,13 +5021,18 @@
           <t>gaming</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K90" s="3" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>atx, dual-chamber, frameless, gaming, micro-atx, mini-itx, modular, pink, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4622,15 +5073,20 @@
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
+          <t>atx, black, compact, gaming, mid-tower, radiator-support, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
           <t>50+ bought in past month</t>
         </is>
       </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K91" s="5" t="inlineStr">
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4669,13 +5125,18 @@
           <t>eclipse-pk</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>gaming, honeycomb-mesh, mid-tower, mini-itx, pink, red, rgb-lighting, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4714,13 +5175,18 @@
           <t>design</t>
         </is>
       </c>
-      <c r="I93" s="4" t="inlineStr"/>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K93" s="5" t="inlineStr">
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>atx, gaming</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr"/>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L93" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4759,13 +5225,18 @@
           <t>f3</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>atx, gaming, high-airflow, mesh-front, micro-atx, red, rgb-lighting, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4804,13 +5275,18 @@
           <t>observatory</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr"/>
-      <c r="J95" s="4" t="inlineStr">
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr"/>
+      <c r="K95" s="4" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K95" s="5" t="inlineStr">
+      <c r="L95" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4849,13 +5325,18 @@
           <t>magnetic</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>magnetic-filters, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4894,13 +5375,18 @@
           <t>f100</t>
         </is>
       </c>
-      <c r="I97" s="4" t="inlineStr"/>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="inlineStr">
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, micro-atx, mini-itx, panoramic-glass, radiator-support, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr"/>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4937,13 +5423,18 @@
           <t>academy</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, micro-atx</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -4982,13 +5473,18 @@
           <t>vx-310</t>
         </is>
       </c>
-      <c r="I99" s="4" t="inlineStr"/>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="inlineStr">
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, mid-tower, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr"/>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5027,13 +5523,18 @@
           <t>bolt</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, high-airflow, mesh-front, micro-atx, radiator-support, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5072,13 +5573,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I101" s="4" t="inlineStr"/>
-      <c r="J101" s="4" t="inlineStr">
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>black, mid-tower</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr"/>
+      <c r="K101" s="4" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K101" s="5" t="inlineStr">
+      <c r="L101" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5117,13 +5623,18 @@
           <t>s2</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>black, e-atx, mid-tower, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5160,13 +5671,18 @@
           <t>open</t>
         </is>
       </c>
-      <c r="I103" s="4" t="inlineStr"/>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K103" s="5" t="inlineStr">
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>atx, mini-itx</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr"/>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L103" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5205,13 +5721,18 @@
           <t>celsius</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K104" s="3" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, compact, gaming, high-airflow, micro-atx, panoramic-glass, red, rgb-lighting, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5250,13 +5771,18 @@
           <t>destroyer</t>
         </is>
       </c>
-      <c r="I105" s="4" t="inlineStr"/>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K105" s="5" t="inlineStr">
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, e-atx, gaming, high-airflow, mid-tower, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr"/>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5295,13 +5821,18 @@
           <t>eclipse</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K106" s="3" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>atx, dual-chamber, gaming, micro-atx, mini-itx, panoramic-glass, red, rgb-lighting, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5340,13 +5871,18 @@
           <t>solar</t>
         </is>
       </c>
-      <c r="I107" s="4" t="inlineStr"/>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K107" s="5" t="inlineStr">
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>atx, gaming, mesh-front, micro-atx, panoramic-glass, radiator-support, red, rgb-lighting, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr"/>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5385,13 +5921,18 @@
           <t>kz-900</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K108" s="3" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, mini-itx, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5430,13 +5971,18 @@
           <t>rb-2</t>
         </is>
       </c>
-      <c r="I109" s="4" t="inlineStr"/>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K109" s="5" t="inlineStr">
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, mesh-front, red, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr"/>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L109" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5475,13 +6021,18 @@
           <t>infinity</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K110" s="3" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, mid-tower, red, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5520,13 +6071,18 @@
           <t>gaming</t>
         </is>
       </c>
-      <c r="I111" s="4" t="inlineStr"/>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K111" s="5" t="inlineStr">
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, dual-chamber, gaming, high-airflow, mid-tower, radiator-support, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr"/>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L111" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5565,13 +6121,18 @@
           <t>v5</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>atx, compact</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K112" s="3" t="inlineStr">
+      <c r="L112" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5610,13 +6171,18 @@
           <t>valkyrie</t>
         </is>
       </c>
-      <c r="I113" s="4" t="inlineStr"/>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K113" s="5" t="inlineStr">
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, high-airflow, mid-tower, red, rgb-lighting, side-panel-glass, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr"/>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5655,13 +6221,18 @@
           <t>is3</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K114" s="3" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>atx, gaming, micro-atx, pink, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5696,13 +6267,18 @@
           <t>d41</t>
         </is>
       </c>
-      <c r="I115" s="4" t="inlineStr"/>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K115" s="5" t="inlineStr">
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>atx, red, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr"/>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5737,13 +6313,18 @@
           <t>t6</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K116" s="3" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>mini-itx</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5778,13 +6359,18 @@
           <t>p500a</t>
         </is>
       </c>
-      <c r="I117" s="4" t="inlineStr"/>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K117" s="5" t="inlineStr">
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>black, mid-tower</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr"/>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5819,13 +6405,18 @@
           <t>klm-002</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, gray, micro-atx</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5860,13 +6451,18 @@
           <t>tk-1</t>
         </is>
       </c>
-      <c r="I119" s="4" t="inlineStr"/>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K119" s="5" t="inlineStr">
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, micro-atx, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr"/>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L119" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5901,13 +6497,18 @@
           <t>d31</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K120" s="3" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>atx, micro-atx, red, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5942,13 +6543,18 @@
           <t>north</t>
         </is>
       </c>
-      <c r="I121" s="4" t="inlineStr"/>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K121" s="5" t="inlineStr">
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>black, mid-tower</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -5983,13 +6589,18 @@
           <t>unity</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K122" s="3" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>black, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6024,13 +6635,18 @@
           <t>enthoo</t>
         </is>
       </c>
-      <c r="I123" s="4" t="inlineStr"/>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K123" s="5" t="inlineStr">
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>black, full-tower</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr"/>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6065,13 +6681,18 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K124" s="3" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>black, mini-itx, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6106,13 +6727,18 @@
           <t>d32</t>
         </is>
       </c>
-      <c r="I125" s="4" t="inlineStr"/>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K125" s="5" t="inlineStr">
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, mesh-front, micro-atx, mini-itx</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr"/>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6147,13 +6773,18 @@
           <t>p500c</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K126" s="3" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>black, mid-tower</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6188,13 +6819,18 @@
           <t>g370a</t>
         </is>
       </c>
-      <c r="I127" s="4" t="inlineStr"/>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr">
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, mid-tower</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr"/>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6229,13 +6865,18 @@
           <t>cx600m</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K128" s="3" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, gaming, micro-atx, wood</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6270,13 +6911,18 @@
           <t>3200d</t>
         </is>
       </c>
-      <c r="I129" s="4" t="inlineStr"/>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K129" s="5" t="inlineStr">
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>mid-tower</t>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr"/>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L129" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6311,13 +6957,18 @@
           <t>802</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K130" s="3" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>black, quiet-design</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6352,13 +7003,18 @@
           <t>tk-4</t>
         </is>
       </c>
-      <c r="I131" s="4" t="inlineStr"/>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K131" s="5" t="inlineStr">
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>atx, curved-design, red, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr"/>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6393,13 +7049,18 @@
           <t>x400</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K132" s="3" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>atx, mid-tower, red, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6434,13 +7095,18 @@
           <t>z20</t>
         </is>
       </c>
-      <c r="I133" s="4" t="inlineStr"/>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K133" s="5" t="inlineStr">
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>atx, mesh-front, micro-atx, mini-itx, white</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr"/>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6475,13 +7141,18 @@
           <t>stronghold</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K134" s="3" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>gray, metal</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6516,13 +7187,18 @@
           <t>501</t>
         </is>
       </c>
-      <c r="I135" s="4" t="inlineStr"/>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K135" s="5" t="inlineStr">
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>black, mid-tower, quiet-design</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr"/>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L135" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6557,13 +7233,18 @@
           <t>206</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K136" s="3" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>mid-tower, white</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6598,13 +7279,18 @@
           <t>901</t>
         </is>
       </c>
-      <c r="I137" s="4" t="inlineStr"/>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K137" s="5" t="inlineStr">
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>full-tower, quiet-design, red, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr"/>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L137" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6639,13 +7325,18 @@
           <t>d520a</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K138" s="3" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>black, mid-tower</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6680,13 +7371,18 @@
           <t>420</t>
         </is>
       </c>
-      <c r="I139" s="4" t="inlineStr"/>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K139" s="5" t="inlineStr">
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>black, mid-tower</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr"/>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L139" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6721,13 +7417,18 @@
           <t>umx3</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K140" s="3" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, micro-atx</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6762,13 +7463,18 @@
           <t>d401</t>
         </is>
       </c>
-      <c r="I141" s="4" t="inlineStr"/>
-      <c r="J141" s="4" t="inlineStr">
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>atx, mid-tower</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr"/>
+      <c r="K141" s="4" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K141" s="5" t="inlineStr">
+      <c r="L141" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6803,13 +7509,18 @@
           <t>d200</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K142" s="3" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>atx, gaming, micro-atx, white</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6844,13 +7555,18 @@
           <t>kz02</t>
         </is>
       </c>
-      <c r="I143" s="4" t="inlineStr"/>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K143" s="5" t="inlineStr">
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>atx, gaming, high-airflow, mid-tower, red, rgb-lighting, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr"/>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L143" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6885,13 +7601,18 @@
           <t>6500d</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K144" s="3" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>dual-chamber, high-airflow, mid-tower, white</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6926,13 +7647,18 @@
           <t>300r</t>
         </is>
       </c>
-      <c r="I145" s="4" t="inlineStr"/>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K145" s="5" t="inlineStr">
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>atx, gaming, high-airflow, mid-tower, radiator-support, white</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr"/>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L145" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -6968,12 +7694,13 @@
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K146" s="3" t="inlineStr">
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7008,13 +7735,18 @@
           <t>500</t>
         </is>
       </c>
-      <c r="I147" s="4" t="inlineStr"/>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K147" s="5" t="inlineStr">
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>black, quiet-design</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr"/>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L147" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7049,13 +7781,18 @@
           <t>mod-3</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K148" s="3" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>atx, micro-atx, mini-itx, red, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7090,13 +7827,18 @@
           <t>rocket</t>
         </is>
       </c>
-      <c r="I149" s="4" t="inlineStr"/>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K149" s="5" t="inlineStr">
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>aluminum, gray, metal, mini-itx</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr"/>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L149" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7131,13 +7873,18 @@
           <t>bo400cg</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>atx, curved-design, gray, metal, mid-tower</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7172,13 +7919,18 @@
           <t>epoch</t>
         </is>
       </c>
-      <c r="I151" s="4" t="inlineStr"/>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K151" s="5" t="inlineStr">
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t>black, mid-tower</t>
+        </is>
+      </c>
+      <c r="J151" s="4" t="inlineStr"/>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L151" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7213,13 +7965,18 @@
           <t>rm3-black/window</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K152" s="3" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, micro-atx</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7254,13 +8011,18 @@
           <t>5000t</t>
         </is>
       </c>
-      <c r="I153" s="4" t="inlineStr"/>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K153" s="5" t="inlineStr">
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>mid-tower, red, rgb-lighting, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr"/>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L153" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7295,13 +8057,18 @@
           <t>320r</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K154" s="3" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>high-airflow, mid-tower, white</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7336,13 +8103,18 @@
           <t>481</t>
         </is>
       </c>
-      <c r="I155" s="4" t="inlineStr"/>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K155" s="5" t="inlineStr">
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t>mini-itx, wood</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr"/>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L155" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7377,13 +8149,18 @@
           <t>t9</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K156" s="3" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>mini-itx, small-form-factor</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7418,13 +8195,18 @@
           <t>horizon</t>
         </is>
       </c>
-      <c r="I157" s="4" t="inlineStr"/>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K157" s="5" t="inlineStr">
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>black, gaming, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J157" s="4" t="inlineStr"/>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L157" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7459,13 +8241,18 @@
           <t>k7</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K158" s="3" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>black, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7500,13 +8287,18 @@
           <t>v2</t>
         </is>
       </c>
-      <c r="I159" s="4" t="inlineStr"/>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K159" s="5" t="inlineStr">
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t>atx</t>
+        </is>
+      </c>
+      <c r="J159" s="4" t="inlineStr"/>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L159" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7541,13 +8333,18 @@
           <t>v150</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K160" s="3" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, micro-atx, mini-itx, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7582,13 +8379,18 @@
           <t>205m</t>
         </is>
       </c>
-      <c r="I161" s="4" t="inlineStr"/>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K161" s="5" t="inlineStr">
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>atx, mesh-front, micro-atx, white</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr"/>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L161" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7623,13 +8425,18 @@
           <t>502</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K162" s="3" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>mid-tower, red, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7665,12 +8472,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr"/>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K163" s="5" t="inlineStr">
+      <c r="J163" s="4" t="inlineStr"/>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L163" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7705,13 +8513,18 @@
           <t>tranquility</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K164" s="3" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>black, quiet-design</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7746,13 +8559,18 @@
           <t>a4-h2o</t>
         </is>
       </c>
-      <c r="I165" s="4" t="inlineStr"/>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K165" s="5" t="inlineStr">
+      <c r="I165" s="4" t="inlineStr">
+        <is>
+          <t>mini-itx</t>
+        </is>
+      </c>
+      <c r="J165" s="4" t="inlineStr"/>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L165" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7787,13 +8605,18 @@
           <t>701</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K166" s="3" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>mid-tower, quiet-design, white</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7828,13 +8651,18 @@
           <t>gladiator</t>
         </is>
       </c>
-      <c r="I167" s="4" t="inlineStr"/>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K167" s="5" t="inlineStr">
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>mid-tower, rgb-lighting</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr"/>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L167" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7869,13 +8697,18 @@
           <t>v12</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K168" s="3" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>atx, micro-atx, mini-itx, panoramic-glass, white</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7910,13 +8743,18 @@
           <t>cs-103</t>
         </is>
       </c>
-      <c r="I169" s="4" t="inlineStr"/>
-      <c r="J169" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K169" s="5" t="inlineStr">
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>black, mini-itx</t>
+        </is>
+      </c>
+      <c r="J169" s="4" t="inlineStr"/>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L169" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7951,13 +8789,18 @@
           <t>g500a</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K170" s="3" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>mid-tower, rgb-lighting, white</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -7992,13 +8835,18 @@
           <t>5000x</t>
         </is>
       </c>
-      <c r="I171" s="4" t="inlineStr"/>
-      <c r="J171" s="4" t="inlineStr">
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t>atx, mid-tower, red, rgb-lighting, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J171" s="4" t="inlineStr"/>
+      <c r="K171" s="4" t="inlineStr">
         <is>
           <t>Amazon, Overclockers</t>
         </is>
       </c>
-      <c r="K171" s="5" t="inlineStr">
+      <c r="L171" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8033,13 +8881,18 @@
           <t>360</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K172" s="3" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>mid-tower, white</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8074,13 +8927,18 @@
           <t>tk-2</t>
         </is>
       </c>
-      <c r="I173" s="4" t="inlineStr"/>
-      <c r="J173" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K173" s="5" t="inlineStr">
+      <c r="I173" s="4" t="inlineStr">
+        <is>
+          <t>black, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J173" s="4" t="inlineStr"/>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L173" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8115,13 +8973,18 @@
           <t>nv7</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K174" s="3" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>full-tower, rgb-lighting, white</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8156,13 +9019,18 @@
           <t>tk-0</t>
         </is>
       </c>
-      <c r="I175" s="4" t="inlineStr"/>
-      <c r="J175" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K175" s="5" t="inlineStr">
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t>mini-itx, red, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J175" s="4" t="inlineStr"/>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L175" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8197,13 +9065,18 @@
           <t>bo400</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K176" s="3" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>aluminum, atx, black, mid-tower, mini-itx, red, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8238,13 +9111,18 @@
           <t>pc-tu150a</t>
         </is>
       </c>
-      <c r="I177" s="4" t="inlineStr"/>
-      <c r="J177" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K177" s="5" t="inlineStr">
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>aluminum, mini-itx</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr"/>
+      <c r="K177" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L177" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8279,13 +9157,18 @@
           <t>9000d</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K178" s="3" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>high-airflow, rgb-lighting, white</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8320,13 +9203,18 @@
           <t>pc-tu150wx</t>
         </is>
       </c>
-      <c r="I179" s="4" t="inlineStr"/>
-      <c r="J179" s="4" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K179" s="5" t="inlineStr">
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>aluminum, black, mini-itx</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr"/>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L179" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8361,13 +9249,18 @@
           <t>420mm</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K180" s="3" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>atx, black, mid-tower, panoramic-glass, red, tempered-glass, usb-type-c</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8402,13 +9295,18 @@
           <t>argb</t>
         </is>
       </c>
-      <c r="I181" s="4" t="inlineStr"/>
-      <c r="J181" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K181" s="5" t="inlineStr">
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t>atx, gaming, mid-tower, panoramic-glass, radiator-support, red, rgb-lighting, tempered-glass, white</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr"/>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L181" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8443,13 +9341,18 @@
           <t>tk-5</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K182" s="3" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>atx, mid-tower, white</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8484,13 +9387,18 @@
           <t>volt</t>
         </is>
       </c>
-      <c r="I183" s="4" t="inlineStr"/>
-      <c r="J183" s="4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="K183" s="5" t="inlineStr">
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>atx, black, compact, gaming, micro-atx, radiator-support, red, rgb-lighting, tempered-glass</t>
+        </is>
+      </c>
+      <c r="J183" s="4" t="inlineStr"/>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L183" s="5" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8525,13 +9433,18 @@
           <t>205</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr">
-        <is>
-          <t>Overclockers</t>
-        </is>
-      </c>
-      <c r="K184" s="3" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>mesh-front, mid-tower, white</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>Overclockers</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr">
         <is>
           <t>View</t>
         </is>
@@ -8539,189 +9452,189 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K155" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K162" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K173" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K175" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId183"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
